--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/FLORIDA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/FLORIDA_2011.xlsx
@@ -967,7 +967,7 @@
         <v>23</v>
       </c>
       <c r="D34">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="35">
@@ -2227,7 +2227,7 @@
         <v>23</v>
       </c>
       <c r="D104">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="105">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C200">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C229">
@@ -4783,7 +4783,7 @@
         <v>23</v>
       </c>
       <c r="D246">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="247">
@@ -5917,7 +5917,7 @@
         <v>23</v>
       </c>
       <c r="D309">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="310">
@@ -6475,7 +6475,7 @@
         <v>23</v>
       </c>
       <c r="D340">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="341">
@@ -10237,7 +10237,7 @@
         <v>23</v>
       </c>
       <c r="D549">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="550">
@@ -12037,7 +12037,7 @@
         <v>23</v>
       </c>
       <c r="D649">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="650">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C762">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C870">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C871">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C912">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C913">
@@ -20479,7 +20479,7 @@
         <v>23</v>
       </c>
       <c r="D1118">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="1119">
@@ -21235,7 +21235,7 @@
         <v>23</v>
       </c>
       <c r="D1160">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="1161">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1319">
@@ -25969,7 +25969,7 @@
         <v>23</v>
       </c>
       <c r="D1423">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
     <row r="1424">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1466">
@@ -27967,7 +27967,7 @@
         <v>23</v>
       </c>
       <c r="D1534">
-        <v>0.000932533246837</v>
+        <v>0.0009325332468370002</v>
       </c>
     </row>
   </sheetData>
